--- a/YOY_venue_comparison.xlsx
+++ b/YOY_venue_comparison.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -449,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LYV Owned &amp; Operated (Fuzzy‑matched) – Shows Announced by Cutoff</t>
+          <t>LYV Owned &amp; Operated (Fuzzy‑matched)</t>
         </is>
       </c>
     </row>
@@ -506,108 +506,227 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Venue Breakdown – Announced by Cutoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2024 Count</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2025 Count</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Arena</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>144</v>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Amphitheatre</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>961</v>
+        <v>128</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>912</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>Amphitheatre</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>20</v>
+        <v>912</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Stadium</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Theater</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>208</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Theater</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>1341</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1347</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Venue Breakdown – All Shows (No Cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2024 Count</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2025 Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>962</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1368</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1485</v>
       </c>
     </row>
   </sheetData>
@@ -621,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -633,7 +752,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>All Shows (All Venues) – Shows Announced by Cutoff</t>
+          <t>All Shows (All Venues)</t>
         </is>
       </c>
     </row>
@@ -690,108 +809,227 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Venue Breakdown – Announced by Cutoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2024 Count</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2025 Count</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Arena</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>912</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>803</v>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Amphitheatre</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1057</v>
+        <v>912</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>963</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>Amphitheatre</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>196</v>
+        <v>1057</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>353</v>
+        <v>963</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Stadium</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>49</v>
+        <v>196</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>71</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Theater</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>499</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>484</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Theater</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1600</v>
+        <v>499</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1580</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>4313</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>4254</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Venue Breakdown – All Shows (No Cutoff)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2024 Count</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2025 Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>942</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>1059</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>541</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1656</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>4467</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4660</v>
       </c>
     </row>
   </sheetData>
